--- a/Codelist Excel Files and Conversion Templates to XML/grp-astmD2488.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/grp-astmD2488.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC8B29D-ADBA-D743-B46A-90C2A80C66D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFF33AA-62F6-4244-AFD1-EE90C0CC65A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14900" yWindow="4860" windowWidth="35840" windowHeight="20740" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -851,9 +851,6 @@
     <t>ASTM D2488</t>
   </si>
   <si>
-    <t>//diggs:Lithology/diggs:classificationSymbol</t>
-  </si>
-  <si>
     <t>classificationSymbol</t>
   </si>
   <si>
@@ -888,6 +885,9 @@
   </si>
   <si>
     <t>grp-astmD2488</t>
+  </si>
+  <si>
+    <t>//diggs:LithologyObservation//diggs:classificationSymbol</t>
   </si>
 </sst>
 </file>
@@ -1091,59 +1091,6 @@
   </cellStyles>
   <dxfs count="20">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1244,6 +1191,59 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
@@ -1262,6 +1262,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="DictionaryName"/>
@@ -1282,53 +1283,53 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:E3" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="12"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H22" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H22" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:H22" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H22">
     <sortCondition ref="B1:B22"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="7">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2735,1,FALSE)),"Not used","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D22" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D22" totalsRowShown="0" headerRowDxfId="19">
   <autoFilter ref="A1:D22" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C2">
     <sortCondition ref="C1:C2"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="18">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,Definitions!B$2:B$1731,1,FALSE)),"Not listed","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SourceElement" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SourceElement" dataDxfId="16"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="ConditionalElement"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1652,16 +1653,16 @@
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="B3" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -1737,7 +1738,7 @@
         <v>269</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1761,7 +1762,7 @@
         <v>269</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1785,7 +1786,7 @@
         <v>269</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1809,7 +1810,7 @@
         <v>269</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1833,7 +1834,7 @@
         <v>269</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1848,7 +1849,7 @@
         <v>242</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>4</v>
@@ -1857,7 +1858,7 @@
         <v>269</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1881,7 +1882,7 @@
         <v>269</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1905,7 +1906,7 @@
         <v>269</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1920,7 +1921,7 @@
         <v>246</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>4</v>
@@ -1929,7 +1930,7 @@
         <v>269</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1953,7 +1954,7 @@
         <v>269</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -1977,7 +1978,7 @@
         <v>269</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -2001,7 +2002,7 @@
         <v>269</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -2010,13 +2011,13 @@
         <v/>
       </c>
       <c r="B14" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>276</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>277</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>4</v>
@@ -2025,7 +2026,7 @@
         <v>269</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -2049,7 +2050,7 @@
         <v>269</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -2073,7 +2074,7 @@
         <v>269</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -2097,7 +2098,7 @@
         <v>269</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -2112,7 +2113,7 @@
         <v>258</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>4</v>
@@ -2121,7 +2122,7 @@
         <v>269</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -2145,7 +2146,7 @@
         <v>269</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -2169,7 +2170,7 @@
         <v>269</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -2184,7 +2185,7 @@
         <v>262</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>4</v>
@@ -2193,7 +2194,7 @@
         <v>269</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="34" x14ac:dyDescent="0.2">
@@ -2217,7 +2218,7 @@
         <v>269</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -2283,7 +2284,7 @@
         <v>233</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2295,7 +2296,7 @@
         <v>235</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2307,7 +2308,7 @@
         <v>237</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2319,7 +2320,7 @@
         <v>239</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2331,7 +2332,7 @@
         <v>241</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2343,7 +2344,7 @@
         <v>242</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2355,7 +2356,7 @@
         <v>243</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2367,7 +2368,7 @@
         <v>244</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2379,7 +2380,7 @@
         <v>246</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2391,7 +2392,7 @@
         <v>247</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2403,7 +2404,7 @@
         <v>249</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2415,7 +2416,7 @@
         <v>251</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2427,7 +2428,7 @@
         <v>253</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2439,7 +2440,7 @@
         <v>255</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2451,7 +2452,7 @@
         <v>257</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2463,7 +2464,7 @@
         <v>258</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2475,7 +2476,7 @@
         <v>259</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2487,7 +2488,7 @@
         <v>260</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2499,7 +2500,7 @@
         <v>262</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2511,7 +2512,7 @@
         <v>263</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2520,10 +2521,10 @@
         <v/>
       </c>
       <c r="B22" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
